--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ64"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5272,10 +5272,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129475963</v>
+        <v>137542161</v>
       </c>
       <c r="B43" t="n">
-        <v>79946</v>
+        <v>79296</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5283,37 +5283,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Väster om Nysäterkölen, Dlr</t>
+          <t>Hammarskaftet, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>404602</v>
+        <v>405060</v>
       </c>
       <c r="R43" t="n">
-        <v>6796090</v>
+        <v>6795566</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5337,22 +5337,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5367,24 +5367,24 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475963</t>
+          <t>https://artportalen.se/Sighting/137542161</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129475964</v>
+        <v>129475963</v>
       </c>
       <c r="B44" t="n">
         <v>79946</v>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>405045</v>
+        <v>404602</v>
       </c>
       <c r="R44" t="n">
-        <v>6795657</v>
+        <v>6796090</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5490,13 +5490,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475964</t>
+          <t>https://artportalen.se/Sighting/129475963</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129475965</v>
+        <v>129475964</v>
       </c>
       <c r="B45" t="n">
         <v>79946</v>
@@ -5531,10 +5531,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>405075</v>
+        <v>405045</v>
       </c>
       <c r="R45" t="n">
-        <v>6795660</v>
+        <v>6795657</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5602,13 +5602,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475965</t>
+          <t>https://artportalen.se/Sighting/129475964</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129475966</v>
+        <v>129475965</v>
       </c>
       <c r="B46" t="n">
         <v>79946</v>
@@ -5643,10 +5643,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>405049</v>
+        <v>405075</v>
       </c>
       <c r="R46" t="n">
-        <v>6795727</v>
+        <v>6795660</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5714,13 +5714,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475966</t>
+          <t>https://artportalen.se/Sighting/129475965</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129475968</v>
+        <v>129475966</v>
       </c>
       <c r="B47" t="n">
         <v>79946</v>
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>405003</v>
+        <v>405049</v>
       </c>
       <c r="R47" t="n">
-        <v>6795853</v>
+        <v>6795727</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5826,13 +5826,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475968</t>
+          <t>https://artportalen.se/Sighting/129475966</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129475969</v>
+        <v>129475968</v>
       </c>
       <c r="B48" t="n">
         <v>79946</v>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404983</v>
+        <v>405003</v>
       </c>
       <c r="R48" t="n">
-        <v>6795860</v>
+        <v>6795853</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5938,13 +5938,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475969</t>
+          <t>https://artportalen.se/Sighting/129475968</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129475970</v>
+        <v>129475969</v>
       </c>
       <c r="B49" t="n">
         <v>79946</v>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404726</v>
+        <v>404983</v>
       </c>
       <c r="R49" t="n">
-        <v>6795995</v>
+        <v>6795860</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6050,13 +6050,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475970</t>
+          <t>https://artportalen.se/Sighting/129475969</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129475971</v>
+        <v>129475970</v>
       </c>
       <c r="B50" t="n">
         <v>79946</v>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404652</v>
+        <v>404726</v>
       </c>
       <c r="R50" t="n">
-        <v>6796177</v>
+        <v>6795995</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6162,16 +6162,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475971</t>
+          <t>https://artportalen.se/Sighting/129475970</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129475981</v>
+        <v>129475971</v>
       </c>
       <c r="B51" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6179,21 +6179,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6203,10 +6203,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404597</v>
+        <v>404652</v>
       </c>
       <c r="R51" t="n">
-        <v>6795875</v>
+        <v>6796177</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6274,13 +6274,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475981</t>
+          <t>https://artportalen.se/Sighting/129475971</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129475982</v>
+        <v>129475981</v>
       </c>
       <c r="B52" t="n">
         <v>79085</v>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404585</v>
+        <v>404597</v>
       </c>
       <c r="R52" t="n">
-        <v>6795876</v>
+        <v>6795875</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6386,13 +6386,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475982</t>
+          <t>https://artportalen.se/Sighting/129475981</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129475983</v>
+        <v>129475982</v>
       </c>
       <c r="B53" t="n">
         <v>79085</v>
@@ -6427,10 +6427,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404762</v>
+        <v>404585</v>
       </c>
       <c r="R53" t="n">
-        <v>6795619</v>
+        <v>6795876</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6498,13 +6498,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475983</t>
+          <t>https://artportalen.se/Sighting/129475982</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129475984</v>
+        <v>129475983</v>
       </c>
       <c r="B54" t="n">
         <v>79085</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404976</v>
+        <v>404762</v>
       </c>
       <c r="R54" t="n">
-        <v>6795654</v>
+        <v>6795619</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6610,13 +6610,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475984</t>
+          <t>https://artportalen.se/Sighting/129475983</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129475985</v>
+        <v>129475984</v>
       </c>
       <c r="B55" t="n">
         <v>79085</v>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404902</v>
+        <v>404976</v>
       </c>
       <c r="R55" t="n">
-        <v>6795911</v>
+        <v>6795654</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6722,13 +6722,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475985</t>
+          <t>https://artportalen.se/Sighting/129475984</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129475986</v>
+        <v>129475985</v>
       </c>
       <c r="B56" t="n">
         <v>79085</v>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404709</v>
+        <v>404902</v>
       </c>
       <c r="R56" t="n">
-        <v>6795944</v>
+        <v>6795911</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6834,13 +6834,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475986</t>
+          <t>https://artportalen.se/Sighting/129475985</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129475988</v>
+        <v>129475986</v>
       </c>
       <c r="B57" t="n">
         <v>79085</v>
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404648</v>
+        <v>404709</v>
       </c>
       <c r="R57" t="n">
-        <v>6796068</v>
+        <v>6795944</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6946,13 +6946,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475988</t>
+          <t>https://artportalen.se/Sighting/129475986</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129475989</v>
+        <v>129475988</v>
       </c>
       <c r="B58" t="n">
         <v>79085</v>
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404659</v>
+        <v>404648</v>
       </c>
       <c r="R58" t="n">
-        <v>6796150</v>
+        <v>6796068</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7058,16 +7058,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475989</t>
+          <t>https://artportalen.se/Sighting/129475988</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129475972</v>
+        <v>129475989</v>
       </c>
       <c r="B59" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7075,21 +7075,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>404620</v>
+        <v>404659</v>
       </c>
       <c r="R59" t="n">
-        <v>6795717</v>
+        <v>6796150</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7170,16 +7170,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475972</t>
+          <t>https://artportalen.se/Sighting/129475989</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129475973</v>
+        <v>137542162</v>
       </c>
       <c r="B60" t="n">
-        <v>79917</v>
+        <v>79297</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7187,37 +7187,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Väster om Nysäterkölen, Dlr</t>
+          <t>Hammarskaftet, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404770</v>
+        <v>405103</v>
       </c>
       <c r="R60" t="n">
-        <v>6795623</v>
+        <v>6795576</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7241,22 +7241,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7271,24 +7271,24 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475973</t>
+          <t>https://artportalen.se/Sighting/137542162</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129475974</v>
+        <v>129475972</v>
       </c>
       <c r="B61" t="n">
         <v>79917</v>
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>405050</v>
+        <v>404620</v>
       </c>
       <c r="R61" t="n">
-        <v>6795647</v>
+        <v>6795717</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7394,13 +7394,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475974</t>
+          <t>https://artportalen.se/Sighting/129475972</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129475975</v>
+        <v>129475973</v>
       </c>
       <c r="B62" t="n">
         <v>79917</v>
@@ -7435,10 +7435,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>405119</v>
+        <v>404770</v>
       </c>
       <c r="R62" t="n">
-        <v>6795655</v>
+        <v>6795623</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7506,13 +7506,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475975</t>
+          <t>https://artportalen.se/Sighting/129475973</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129475976</v>
+        <v>129475974</v>
       </c>
       <c r="B63" t="n">
         <v>79917</v>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>405003</v>
+        <v>405050</v>
       </c>
       <c r="R63" t="n">
-        <v>6795853</v>
+        <v>6795647</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7582,7 +7582,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7618,13 +7618,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129475976</t>
+          <t>https://artportalen.se/Sighting/129475974</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129475977</v>
+        <v>129475975</v>
       </c>
       <c r="B64" t="n">
         <v>79917</v>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>404709</v>
+        <v>405119</v>
       </c>
       <c r="R64" t="n">
-        <v>6795945</v>
+        <v>6795655</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7729,6 +7729,230 @@
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475975</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129475976</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Väster om Nysäterkölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>405003</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6795853</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475976</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129475977</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Väster om Nysäterkölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>404709</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6795945</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129475977</t>
         </is>
@@ -7799,6 +8023,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
